--- a/survey_templates/032_new_product_taste_preferences_questionnaire--survey_templates.xlsx
+++ b/survey_templates/032_new_product_taste_preferences_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dark',_'value':_'dark'}</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dark', 'value': 'Dark'}</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red',_'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Red', 'value': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blue',_'value':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Blue', 'value': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green',_'value':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green', 'value': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strong',_'value':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strong', 'value': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mild',_'value':_'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mild', 'value': 'Mild'}</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sweet',_'value':_'sweet'}</t>
+          <t>sweet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sweet', 'value': 'Sweet'}</t>
+          <t>Sweet</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bitter',_'value':_'bitter'}</t>
+          <t>bitter</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bitter', 'value': 'Bitter'}</t>
+          <t>Bitter</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sour',_'value':_'sour'}</t>
+          <t>sour</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sour', 'value': 'Sour'}</t>
+          <t>Sour</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'smooth',_'value':_'smooth'}</t>
+          <t>smooth</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Smooth', 'value': 'Smooth'}</t>
+          <t>Smooth</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rough',_'value':_'rough'}</t>
+          <t>rough</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rough', 'value': 'Rough'}</t>
+          <t>Rough</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'short',_'value':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Short', 'value': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'long',_'value':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Long', 'value': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bottle',_'value':_'bottle'}</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bottle', 'value': 'Bottle'}</t>
+          <t>Bottle</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'can',_'value':_'can'}</t>
+          <t>can</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Can', 'value': 'Can'}</t>
+          <t>Can</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
